--- a/dictionaries/NaturalOne.xlsx
+++ b/dictionaries/NaturalOne.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="623">
   <si>
     <t xml:space="preserve">AC</t>
   </si>
@@ -130,12 +130,6 @@
     <t xml:space="preserve">یار</t>
   </si>
   <si>
-    <t xml:space="preserve">AnOngoingGame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بازی جاری</t>
-  </si>
-  <si>
     <t xml:space="preserve">AnimalHandling</t>
   </si>
   <si>
@@ -407,12 +401,6 @@
   </si>
   <si>
     <t xml:space="preserve">کاندیشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conditions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کاندیشن‌ها</t>
   </si>
   <si>
     <t xml:space="preserve">Constitution</t>
@@ -615,1348 +603,1369 @@
     <t xml:space="preserve">دمیج</t>
   </si>
   <si>
+    <t xml:space="preserve">DamageDice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DamageRoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DamageRolls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس‌های دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DamagingEffect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اتفاقات دمیج‌دار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darkness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاریکی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darkvision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دارک‌ویژن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deafened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Death</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مرگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دسپشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dehydration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کم آبی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dexterity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دکستریتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DexterityCheck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس دکستریتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DexteritySaves</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس نجات دکستریتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DexteritySavingThrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DiceNotationExplanation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DifficultTerrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمین سخت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DifficultyClass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دیفیکالتی کلس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DimLight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نور کم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disadvantage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دیس ادونتیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disengage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دیس اینگیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dodge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">داج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonMaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانجن مستر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonMastersGuide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دانجن مستر گاید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DungeonsAndDragons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لوازم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhaustion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خستگی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گشت و گذار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Falling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سقوط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فیت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویژگی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فینس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آتش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فایر دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireResistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فایر رزیستنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fireball</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FlySpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سرعت پرواز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForgottenRealms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فورگاتن رلمز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دوستانه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frightened</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترسیده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gargantuan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غول پیکر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gargoyle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گارگویل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grappled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گرپلد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grayhawk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گری هاک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Greataxe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تبر جنگی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HalfCover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نیمه کاور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hazard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخاطره</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیل کردن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeavilyObscured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">به شدت پوشیده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کمک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HeroicInspiration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیرویک اینسپریشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخفی شدن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">History</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیستوری</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اچ پی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HolySymbol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نماد مقدس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hostile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خصمانه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گنده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ایمیونیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Incapacitated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بیهوش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indifferent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بی تفاوت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infernal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینفرنال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Influence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینفلوئنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initiative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینیشیتیو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InitiativeOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترتیب اینیشیتیو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InitiativeRoll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس اینیشیتیو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینسایت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینتلجنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IntelligenceCheck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس اینتلجنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intimidation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">انتیمیدیشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اینوستیگیشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invisible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نامرئی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آیتم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پریدن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ladder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نردبان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lantern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فانوس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Large</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بزرگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LightlyObscured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کم پوشیده شده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنج طولانی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LongRest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استراحت طولانی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longbow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کمان بلند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجیک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MagicItem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجیک آیتم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MagicItems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مجیکال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malnutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کم غذایی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MarchingOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترتیب حرکت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaximumHitPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مکس اچ‌پی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaximumHitPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مدیسن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">متوسط</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeleeAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله میلی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeleeAttacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله‌های میلی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MeleeWeapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسلحه میلی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miniature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">منیاتور</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مادیفایر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هیولا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Movement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حرکت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MovementAndPosition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حرکت و جایگاه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ان‌پی‌سی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">۱ طبیعی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">۲۰ طبیعی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nature</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نیچر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NecroticDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نکراتیک دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonMagical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">غیرمجیکال</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NonPlayerCharacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NormalRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنج عادی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جسم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اجسام</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obscured</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پوشیده</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OneShot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وان‌شات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpportunityAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله اپرتونیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OpportunityAttacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله‌های اپرتونیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paralyzed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پارالایزد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perception</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرسپشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرفورمنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Persuasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرسوئیژن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petrified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پتریفاید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PiercingDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پیرسینگ دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlanesOfExistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">صفحات وجود</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlateArmor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زره صفحه‌ای</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Player</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayerCharacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاراکتر پلیر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PlayerHandbook</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیرز هندبوک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Players</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پلیرها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poisoned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پویزند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">موقعیت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PotionOfHealing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پوشن هیلینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفشنسی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProficiencyBonus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بونس پروفشنسی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پرون</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پراپرتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Push</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل دادن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quarterstaff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">عصای چوبی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RadiantDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ریدینت دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شعاع</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RaiseDead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رنج </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RangedAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله رنج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RangedAttacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">حمله‌های رنج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RangedWeapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسلحه رنج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ریچ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ری‌اکشن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ردی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جهان‌ها</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Religion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رلیجن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رزیستنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رستریند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rogue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">روگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Round</t>
+  </si>
+  <si>
+    <t xml:space="preserve">راند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RulesGlossary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">فهرست قوانین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SavingThrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس نجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SavingThrows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس‌های نجات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">امتیاز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SearUndead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سرچ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shield</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سپر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortOrLongRest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استراحت کوتاه یا بلند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ShortRest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استراحت کوتاه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اندازه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SizeCategory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دسته بندی اندازه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مهارت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillProficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفشنسی مهارت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slashing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسلشینگ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SleightOfHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسلایت اف هند</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کوچک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SneakAttack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SocialInteraction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تعامل اجتماعی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Species</t>
+  </si>
+  <si>
+    <t xml:space="preserve">گونه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سرعت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpellSlot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل اسلات</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spellcaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کستر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spellcasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسپل کست کردن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پایدار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StablizingACharacter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پایدار کردن کاراکتر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StatBlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استت بلاک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استلث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استرنث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StrengthCheck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس استرنث</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استادی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stunned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">استان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suffocation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خفگی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سورپرایز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Survival</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سوروایول</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SwimSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سرعت شنا</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swimming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شنا کردن</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sword</t>
+  </si>
+  <si>
+    <t xml:space="preserve">شمشیر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هدف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Targets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اهداف</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teleport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تلپورت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TemporaryHitPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اچ‌پی موقت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TemporaryHitPoints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">زمین</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThievesTools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثیوز تولز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThreeQuarterCover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاور یک سوم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ThunderDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ثاندر دمیج</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thunderwave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کوچولو</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ابزار</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مشعل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalCover</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاور کامل</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tremorsense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ترمورسنس</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تریگر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Truesight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تروسایت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نوبت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TurnBased</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بر اساس نوبت</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnarmedStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">آن‌آرمد استراک</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnarmedStrikes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unconscious</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بی‌هوش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">یوتلایز</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وسیله نقلیه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وسایل نقلیه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VehiclesForSale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وسایل نقلیه برای فروش</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">دید</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulnerability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ولنربیلیتی</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warhammer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وارهمر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">سلاح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WeaponProperties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">پروفشنسی اسلحه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weapons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">اسحه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">خواهان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wisdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزدم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WisdomCheck</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس ویزدم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WisdomChecks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس‌های ویزدم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WisdomSave</t>
+  </si>
+  <si>
+    <t xml:space="preserve">تاس نجات ویزدم</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ویزارد</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AnOngoingGame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بازی جاری</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conditions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">کاندیشن‌ها</t>
+  </si>
+  <si>
     <t xml:space="preserve">DamageAndHealing</t>
   </si>
   <si>
     <t xml:space="preserve">دمیج و هیل</t>
   </si>
   <si>
-    <t xml:space="preserve">DamageDice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DamageRoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DamageRolls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس‌های دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DamagingEffect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اتفاقات دمیج‌دار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darkness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاریکی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darkvision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دارک‌ویژن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dash</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deafened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Death</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مرگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deception</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دسپشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dehydration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کم آبی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dexterity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دکستریتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DexterityCheck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس دکستریتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DexteritySaves</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس نجات دکستریتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DexteritySavingThrow</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dice</t>
   </si>
   <si>
-    <t xml:space="preserve">DiceNotationExplanation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DifficultTerrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">زمین سخت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DifficultyClass</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دیفیکالتی کلس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DimLight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نور کم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disadvantage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دیس ادونتیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disengage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دیس اینگیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dodge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">داج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DungeonMaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دانجن مستر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DungeonMastersGuide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دانجن مستر گاید</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لوازم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exhaustion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خستگی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">گشت و گذار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Falling</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سقوط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فیت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ویژگی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finesse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فینس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آتش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فایر دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireResistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فایر رزیستنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fireball</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FlySpeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سرعت پرواز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ForgottenRealms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فورگاتن رلمز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friendly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دوستانه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frightened</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ترسیده</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gargantuan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غول پیکر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grappled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">گرپلد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grayhawk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">گری هاک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Greataxe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تبر جنگی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HalfCover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نیمه کاور</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hazard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مخاطره</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Healing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیل کردن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HeavilyObscured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">به شدت پوشیده</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کمک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HeroicInspiration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیرویک اینسپریشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مخفی شدن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">History</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیستوری</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اچ پی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HolySymbol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نماد مقدس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hostile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خصمانه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">گنده</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immunity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ایمیونیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Incapacitated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بیهوش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indifferent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بی تفاوت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infernal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینفرنال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Influence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینفلوئنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initiative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینیشیتیو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InitiativeOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ترتیب اینیشیتیو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">InitiativeRoll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس اینیشیتیو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینسایت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intelligence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینتلجنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IntelligenceCheck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس اینتلجنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intimidation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">انتیمیدیشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اینوستیگیشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Invisible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نامرئی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آیتم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jumping</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پریدن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ladder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نردبان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lantern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فانوس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Large</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بزرگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">لول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Light</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نور</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LightlyObscured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کم پوشیده شده</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LongRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رنج طولانی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LongRest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استراحت طولانی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Longbow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کمان بلند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مجیک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MagicItem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مجیک آیتم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MagicItems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مجیکال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Malnutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کم غذایی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MarchingOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ترتیب حرکت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaximumHitPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مکس اچ‌پی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaximumHitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مدیسن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">متوسط</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeleeAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله میلی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeleeAttacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله‌های میلی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MeleeWeapon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسلحه میلی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miniature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">منیاتور</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مادیفایر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هیولا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Movement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حرکت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MovementAndPosition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حرکت و جایگاه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ان‌پی‌سی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">۱ طبیعی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Natural20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">۲۰ طبیعی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nature</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نیچر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NecroticDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نکراتیک دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonMagical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">غیرمجیکال</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NonPlayerCharacter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NormalRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رنج عادی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Object</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جسم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اجسام</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Obscured</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پوشیده</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OneShot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وان‌شات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpportunityAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله اپرتونیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OpportunityAttacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله‌های اپرتونیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paralyzed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پارالایزد</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perception</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پرسپشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پرفورمنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Persuasion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پرسوئیژن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petrified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پتریفاید</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PiercingDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پیرسینگ دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlanesOfExistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">صفحات وجود</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlateArmor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">زره صفحه‌ای</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Player</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پلیر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayerCharacter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کاراکتر پلیر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PlayerHandbook</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پلیرز هندبوک</t>
-  </si>
-  <si>
     <t xml:space="preserve">PlayerOrDm</t>
   </si>
   <si>
     <t xml:space="preserve">پلیر یا ‌دی‌ام؟</t>
   </si>
   <si>
-    <t xml:space="preserve">Players</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پلیرها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poisoned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پویزند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">موقعیت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PotionOfHealing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پوشن هیلینگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پروفشنسی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProficiencyBonus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بونس پروفشنسی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پرون</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پراپرتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Push</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هل دادن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quarterstaff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">عصای چوبی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RadiantDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ریدینت دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شعاع</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RaiseDead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رنج </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RangedAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله رنج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RangedAttacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">حمله‌های رنج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RangedWeapon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسلحه رنج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ریچ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ری‌اکشن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ردی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">جهان‌ها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Religion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رلیجن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رزیستنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">رستریند</t>
-  </si>
-  <si>
     <t xml:space="preserve">RhythmOfPlay</t>
   </si>
   <si>
     <t xml:space="preserve">ریتم بازی</t>
   </si>
   <si>
-    <t xml:space="preserve">Rogue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">روگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Round</t>
-  </si>
-  <si>
-    <t xml:space="preserve">راند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RulesGlossary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">فهرست قوانین</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نجات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SavingThrow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس نجات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SavingThrows</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس‌های نجات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">امتیاز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SearUndead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سرچ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shield</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سپر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ShortOrLongRest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استراحت کوتاه یا بلند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ShortRest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استراحت کوتاه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اندازه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SizeCategory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دسته بندی اندازه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مهارت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkillProficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پروفشنسی مهارت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slashing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسلشینگ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SleightOfHand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسلایت اف هند</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کوچک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SneakAttack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SocialInteraction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تعامل اجتماعی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">گونه‌ها</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سرعت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SpellSlot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل اسلات</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spellcaster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل کستر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spellcasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسپل کست کردن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پایدار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StablizingACharacter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پایدار کردن کاراکتر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StatBlock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استت بلاک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استلث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استرنث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">StrengthCheck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس استرنث</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استادی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stunned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">استان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suffocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خفگی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Surprise</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سورپرایز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Survival</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سوروایول</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SwimSpeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سرعت شنا</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Swimming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شنا کردن</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sword</t>
-  </si>
-  <si>
-    <t xml:space="preserve">شمشیر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">هدف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Targets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اهداف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teleport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تلپورت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TemporaryHitPoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اچ‌پی موقت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TemporaryHitPoints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terrain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">زمین</t>
-  </si>
-  <si>
     <t xml:space="preserve">TheSixAbilities</t>
   </si>
   <si>
     <t xml:space="preserve">شش ابیلیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThievesTools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ثیوز تولز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThreeQuarterCover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کاور یک سوم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ThunderDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ثاندر دمیج</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thunderwave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiny</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کوچولو</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ابزار</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">مشعل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TotalCover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">کاور کامل</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tremorsense</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ترمورسنس</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trigger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تریگر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Truesight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تروسایت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">نوبت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TurnBased</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بر اساس نوبت</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnarmedStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">آن‌آرمد استراک</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnarmedStrikes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unconscious</t>
-  </si>
-  <si>
-    <t xml:space="preserve">بی‌هوش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utilize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">یوتلایز</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وسیله نقلیه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وسایل نقلیه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VehiclesForSale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وسایل نقلیه برای فروش</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">دید</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulnerability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ولنربیلیتی</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warhammer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">وارهمر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">سلاح</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WeaponProperties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">پروفشنسی اسلحه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weapons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">اسحه</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">خواهان</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wisdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ویزدم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WisdomCheck</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس ویزدم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WisdomChecks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس‌های ویزدم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WisdomSave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">تاس نجات ویزدم</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wizard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ویزارد</t>
   </si>
 </sst>
 </file>
@@ -2244,8 +2253,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B320"/>
+  <dimension ref="A1:B323"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.46"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2740,15 +2753,15 @@
         <v>122</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2780,43 +2793,43 @@
         <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>140</v>
       </c>
     </row>
@@ -2833,40 +2846,40 @@
         <v>143</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B76" s="2" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2878,7 +2891,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>154</v>
       </c>
@@ -2886,15 +2899,15 @@
         <v>155</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B82" s="2" t="s">
+      <c r="B82" s="1" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>158</v>
       </c>
@@ -2902,11 +2915,11 @@
         <v>159</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>161</v>
       </c>
     </row>
@@ -2947,31 +2960,31 @@
         <v>170</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3051,28 +3064,25 @@
         <v>195</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>200</v>
@@ -3080,54 +3090,54 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>203</v>
       </c>
+      <c r="B107" s="2" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B112" s="2" t="s">
         <v>213</v>
       </c>
     </row>
@@ -3215,28 +3225,28 @@
       <c r="A123" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>235</v>
-      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>240</v>
       </c>
     </row>
@@ -3605,23 +3615,23 @@
         <v>331</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="B173" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="B174" s="2" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3645,23 +3655,23 @@
         <v>340</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="B178" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="B179" s="2" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3781,23 +3791,23 @@
         <v>373</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>375</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4028,28 +4038,28 @@
       <c r="A225" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>435</v>
-      </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>440</v>
       </c>
     </row>
@@ -4177,36 +4187,36 @@
       <c r="A244" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>472</v>
-      </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B245" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B247" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>479</v>
       </c>
     </row>
@@ -4270,36 +4280,36 @@
       <c r="A256" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>495</v>
-      </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>502</v>
       </c>
     </row>
@@ -4476,83 +4486,83 @@
         <v>545</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>555</v>
-      </c>
     </row>
     <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>564</v>
       </c>
     </row>
@@ -4601,47 +4611,47 @@
         <v>575</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A300" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4741,43 +4751,64 @@
       </c>
     </row>
     <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>611</v>
+      <c r="A316" s="2" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A319" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A320" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A321" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="B320" s="2" t="s">
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A322" s="1" t="s">
         <v>619</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A323" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
